--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487982_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487982_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2305</v>
+        <v>7.0307</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1574</v>
+        <v>4.463</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0731</v>
+        <v>2.5677</v>
       </c>
       <c r="G2" t="n">
         <v>5.7751</v>
@@ -610,13 +610,13 @@
         <v>1.1893</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3163</v>
+        <v>0.1165</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.433</v>
+        <v>-0.1274</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7493</v>
+        <v>0.2439</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0503</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7222</v>
+        <v>3.5465</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4985</v>
+        <v>3.2947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2238</v>
+        <v>0.2518</v>
       </c>
       <c r="G3" t="n">
         <v>0.4482</v>
@@ -688,13 +688,13 @@
         <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3859</v>
+        <v>0.2102</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4664</v>
+        <v>0.2627</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0806</v>
+        <v>-0.0525</v>
       </c>
       <c r="V3" t="n">
         <v>2.2935</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1877</v>
+        <v>2.1481</v>
       </c>
       <c r="E4" t="n">
-        <v>4.51</v>
+        <v>3.695</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3222</v>
+        <v>-1.5469</v>
       </c>
       <c r="G4" t="n">
         <v>5.6076</v>
@@ -766,13 +766,13 @@
         <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3112</v>
+        <v>0.2717</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1345</v>
+        <v>0.3196</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1767</v>
+        <v>-0.0479</v>
       </c>
       <c r="V4" t="n">
         <v>-3.3346</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MUÑOZ LEIVA</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6027</v>
+        <v>0.7278</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6027</v>
+        <v>0.7664</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.0386</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6027</v>
+        <v>0.6775</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.9282</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6027</v>
+        <v>-0.2507</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6027</v>
+        <v>0.4315</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.3032</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6027</v>
+        <v>0.1283</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.379</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.4148</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.2687</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.1461</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. MUÑOZ LEIVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.508</v>
+        <v>0.6027</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1544</v>
+        <v>0.6027</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6464</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9452</v>
+        <v>0.6027</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5222</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4674</v>
+        <v>0.6027</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1532</v>
+        <v>0.6027</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4986</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6545</v>
+        <v>0.6027</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0984</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0235</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1219</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3465</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4109</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0644</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4033</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4033</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4294</v>
+        <v>0.3957</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6645</v>
+        <v>1.1544</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2351</v>
+        <v>-0.7587</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6775</v>
+        <v>-0.9452</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9282</v>
+        <v>0.5222</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2507</v>
+        <v>-1.4674</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4315</v>
+        <v>1.1532</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3032</v>
+        <v>0.4986</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1283</v>
+        <v>0.6545</v>
       </c>
       <c r="M8" t="n">
-        <v>0.246</v>
+        <v>-2.0984</v>
       </c>
       <c r="N8" t="n">
-        <v>0.625</v>
+        <v>0.0235</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.379</v>
+        <v>-2.1219</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.4588</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3706</v>
+        <v>-0.4109</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3426</v>
+        <v>-0.0479</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7243000000000001</v>
+        <v>1.4033</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6036</v>
+        <v>1.4033</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1239</v>
+        <v>0.1134</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0917</v>
+        <v>0.1936</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0322</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5831</v>
@@ -1156,13 +1156,13 @@
         <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3105</v>
+        <v>0.3001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.011</v>
+        <v>0.1129</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2995</v>
+        <v>0.1872</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7511</v>
+        <v>-0.674</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2651</v>
+        <v>-0.4688</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.486</v>
+        <v>-0.2052</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1312</v>
@@ -1234,13 +1234,13 @@
         <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.301</v>
+        <v>-0.2239</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.132</v>
+        <v>-0.3358</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1689</v>
+        <v>0.1119</v>
       </c>
       <c r="V10" t="n">
         <v>0.4828</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0163</v>
+        <v>-2.8302</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6009</v>
+        <v>-1.499</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4154</v>
+        <v>-1.3311</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6187</v>
@@ -1312,13 +1312,13 @@
         <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.131</v>
+        <v>0.0551</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0514</v>
+        <v>0.0505</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0046</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4737</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.65</v>
+        <v>-3.3268</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6636</v>
+        <v>-1.2561</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9864</v>
+        <v>-2.0707</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5837</v>
@@ -1390,13 +1390,13 @@
         <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4012</v>
+        <v>-0.078</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6129</v>
+        <v>-0.2055</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2117</v>
+        <v>0.1275</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2775</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.045</v>
+        <v>-3.9669</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4885</v>
+        <v>-2.7754</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5566</v>
+        <v>-1.1915</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0023</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7058</v>
+        <v>-0.6277</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8515</v>
+        <v>-0.1384</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.4893</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.3206</v>
+        <v>-5.7457</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.192</v>
+        <v>-2.7013</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1287</v>
+        <v>-3.0444</v>
       </c>
       <c r="G14" t="n">
         <v>-4.7491</v>
@@ -1546,13 +1546,13 @@
         <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>0.706</v>
+        <v>0.2809</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8298</v>
+        <v>0.3204</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1238</v>
+        <v>-0.0396</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2775</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7706000000000026</v>
+        <v>-0.7706999999999997</v>
       </c>
       <c r="E15" t="n">
-        <v>6.677099999999999</v>
+        <v>6.677199999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.447699999999999</v>
+        <v>-7.447799999999999</v>
       </c>
       <c r="G15" t="n">
         <v>3.7058</v>
@@ -1606,7 +1606,7 @@
         <v>6.506099999999998</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.679</v>
+        <v>-6.679000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>1.1854</v>
@@ -1624,13 +1624,13 @@
         <v>10.9022</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5688</v>
+        <v>-0.5687</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4206</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1483</v>
+        <v>-0.1482</v>
       </c>
       <c r="V15" t="n">
         <v>-4.8988</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.4554</v>
+        <v>8.134600000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2825</v>
+        <v>6.69</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1729</v>
+        <v>1.4446</v>
       </c>
       <c r="G16" t="n">
         <v>4.2704</v>
@@ -1702,13 +1702,13 @@
         <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1762</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.433</v>
+        <v>-0.0255</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6091</v>
+        <v>0.8808</v>
       </c>
       <c r="V16" t="n">
         <v>2.4142</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0606</v>
+        <v>4.0279</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7998</v>
+        <v>2.5976</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7392</v>
+        <v>1.4304</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0641</v>
+        <v>3.8974</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4296</v>
+        <v>1.9287</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3655</v>
+        <v>1.9687</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4285</v>
+        <v>4.5904</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.712</v>
+        <v>1.9711</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1405</v>
+        <v>2.6193</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4927</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7176</v>
+        <v>-0.0424</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.775</v>
+        <v>-0.6506</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1982</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1893</v>
+        <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5827</v>
+        <v>0.3992</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4062</v>
+        <v>0.0598</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1765</v>
+        <v>0.3394</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3438</v>
+        <v>-0.0704</v>
       </c>
       <c r="W17" t="n">
-        <v>4.1545</v>
+        <v>-0.0704</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8094</v>
+        <v>3.0132</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2919</v>
+        <v>3.883</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5175</v>
+        <v>-0.8698</v>
       </c>
       <c r="G18" t="n">
-        <v>3.8974</v>
+        <v>-1.0641</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9287</v>
+        <v>-1.4296</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9687</v>
+        <v>0.3655</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5904</v>
+        <v>0.4285</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9711</v>
+        <v>-0.712</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6193</v>
+        <v>1.1405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-1.4927</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0424</v>
+        <v>-0.7176</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6506</v>
+        <v>-0.775</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1982</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>-1.1893</v>
       </c>
       <c r="R18" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8193</v>
+        <v>1.5353</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2458</v>
+        <v>0.4894</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5735</v>
+        <v>1.0459</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0704</v>
+        <v>2.3438</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0704</v>
+        <v>4.1545</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.592</v>
+        <v>1.6612</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7436</v>
+        <v>-1.6417</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3356</v>
+        <v>3.303</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4518</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6365</v>
+        <v>0.7057</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0038</v>
+        <v>0.1057</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6327</v>
+        <v>0.6</v>
       </c>
       <c r="V19" t="n">
         <v>1.0109</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9354</v>
+        <v>0.7153</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1492</v>
+        <v>1.7417</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2138</v>
+        <v>-1.0264</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5436</v>
@@ -2092,13 +2092,13 @@
         <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>0.131</v>
+        <v>-0.089</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4333</v>
+        <v>0.0259</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3023</v>
+        <v>-0.1149</v>
       </c>
       <c r="V21" t="n">
         <v>1.3479</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5026</v>
+        <v>0.4804</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0474</v>
+        <v>0.5381</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5448</v>
+        <v>-0.0576</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0517</v>
@@ -2248,13 +2248,13 @@
         <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>1.486</v>
+        <v>1.4637</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9142</v>
+        <v>0.4049</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5717</v>
+        <v>1.0589</v>
       </c>
       <c r="V23" t="n">
         <v>0.8701</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1919</v>
+        <v>-3.0058</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2407</v>
+        <v>-1.1388</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9512</v>
+        <v>-1.867</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1372</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1934</v>
+        <v>-0.0073</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2496</v>
+        <v>-0.1477</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0562</v>
+        <v>0.1404</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8701</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5423</v>
+        <v>-3.3209</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3697</v>
+        <v>-2.0641</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1726</v>
+        <v>-1.2568</v>
       </c>
       <c r="G25" t="n">
         <v>-1.8783</v>
@@ -2404,13 +2404,13 @@
         <v>0.1982</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4515</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5616</v>
+        <v>-0.256</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1113</v>
+        <v>-0.1956</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.8402</v>
+        <v>-3.3955</v>
       </c>
       <c r="E26" t="n">
         <v>-2.76</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0802</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-2.7452</v>
@@ -2482,13 +2482,13 @@
         <v>0.7929</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0862</v>
+        <v>-0.6415</v>
       </c>
       <c r="T26" t="n">
         <v>-0.2458</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8404</v>
+        <v>-0.3957</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6036</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.8209</v>
+        <v>-6.6338</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.8197</v>
+        <v>-2.2085</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.0012</v>
+        <v>-4.4253</v>
       </c>
       <c r="G27" t="n">
         <v>-3.8123</v>
@@ -2560,13 +2560,13 @@
         <v>0.3964</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.6717</v>
+        <v>-0.4845</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8736</v>
+        <v>-0.2623</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.7981</v>
+        <v>-0.2222</v>
       </c>
       <c r="V27" t="n">
         <v>-1.5441</v>
@@ -2593,16 +2593,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7707999999999995</v>
+        <v>3.487299999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>7.447799999999998</v>
+        <v>7.448000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-6.677</v>
+        <v>-3.9605</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.705699999999999</v>
+        <v>-3.705700000000001</v>
       </c>
       <c r="H28" t="n">
         <v>-5.0641</v>
@@ -2629,7 +2629,7 @@
         <v>-6.506</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.9911000000000002</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q28" t="n">
         <v>-10.902</v>
@@ -2638,13 +2638,13 @@
         <v>9.911099999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5689000000000006</v>
+        <v>3.2854</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1481</v>
+        <v>0.1484000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4206000000000003</v>
+        <v>3.137</v>
       </c>
       <c r="V28" t="n">
         <v>4.8987</v>
